--- a/artfynd/A 37928-2025 artfynd.xlsx
+++ b/artfynd/A 37928-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165872</v>
       </c>
       <c r="B2" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129166200</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129166095</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129166096</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129165600</v>
       </c>
       <c r="B6" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129166201</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 37928-2025 artfynd.xlsx
+++ b/artfynd/A 37928-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129166095</v>
+        <v>129165600</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>684110</v>
+        <v>683976</v>
       </c>
       <c r="R4" t="n">
-        <v>7087838</v>
+        <v>7087837</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129166096</v>
+        <v>129166095</v>
       </c>
       <c r="B5" t="n">
         <v>79035</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>684212</v>
+        <v>684110</v>
       </c>
       <c r="R5" t="n">
-        <v>7087694</v>
+        <v>7087838</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129165600</v>
+        <v>129166096</v>
       </c>
       <c r="B6" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683976</v>
+        <v>684212</v>
       </c>
       <c r="R6" t="n">
-        <v>7087837</v>
+        <v>7087694</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 37928-2025 artfynd.xlsx
+++ b/artfynd/A 37928-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129165600</v>
+        <v>129166096</v>
       </c>
       <c r="B4" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683976</v>
+        <v>684212</v>
       </c>
       <c r="R4" t="n">
-        <v>7087837</v>
+        <v>7087694</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129166096</v>
+        <v>129165600</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>684212</v>
+        <v>683976</v>
       </c>
       <c r="R6" t="n">
-        <v>7087694</v>
+        <v>7087837</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 37928-2025 artfynd.xlsx
+++ b/artfynd/A 37928-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165872</v>
       </c>
       <c r="B2" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129166200</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129166096</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129166095</v>
+        <v>129165600</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>684110</v>
+        <v>683976</v>
       </c>
       <c r="R5" t="n">
-        <v>7087838</v>
+        <v>7087837</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129165600</v>
+        <v>129166095</v>
       </c>
       <c r="B6" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683976</v>
+        <v>684110</v>
       </c>
       <c r="R6" t="n">
-        <v>7087837</v>
+        <v>7087838</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1163,7 +1163,7 @@
         <v>129166201</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 37928-2025 artfynd.xlsx
+++ b/artfynd/A 37928-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129166096</v>
+        <v>129165600</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>684212</v>
+        <v>683976</v>
       </c>
       <c r="R4" t="n">
-        <v>7087694</v>
+        <v>7087837</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129165600</v>
+        <v>129166095</v>
       </c>
       <c r="B5" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683976</v>
+        <v>684110</v>
       </c>
       <c r="R5" t="n">
-        <v>7087837</v>
+        <v>7087838</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129166095</v>
+        <v>129166096</v>
       </c>
       <c r="B6" t="n">
         <v>79039</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>684110</v>
+        <v>684212</v>
       </c>
       <c r="R6" t="n">
-        <v>7087838</v>
+        <v>7087694</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 37928-2025 artfynd.xlsx
+++ b/artfynd/A 37928-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165872</v>
       </c>
       <c r="B2" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129166200</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129165600</v>
       </c>
       <c r="B4" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129166095</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129166096</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129166201</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 37928-2025 artfynd.xlsx
+++ b/artfynd/A 37928-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129165600</v>
+        <v>129166095</v>
       </c>
       <c r="B4" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683976</v>
+        <v>684110</v>
       </c>
       <c r="R4" t="n">
-        <v>7087837</v>
+        <v>7087838</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129166095</v>
+        <v>129166096</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>684110</v>
+        <v>684212</v>
       </c>
       <c r="R5" t="n">
-        <v>7087838</v>
+        <v>7087694</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129166096</v>
+        <v>129165600</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>684212</v>
+        <v>683976</v>
       </c>
       <c r="R6" t="n">
-        <v>7087694</v>
+        <v>7087837</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
